--- a/backtest/results_qmt/七星QMT_交易记录_2026.xlsx
+++ b/backtest/results_qmt/七星QMT_交易记录_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G310"/>
+  <dimension ref="A1:G312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10164,6 +10164,72 @@
         </is>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:10</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>2.426</v>
+      </c>
+      <c r="F311" t="n">
+        <v>4.2646</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:10</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>能源化工ETF建信</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>sz159981</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>1.746</v>
+      </c>
+      <c r="F312" t="n">
+        <v>4.3508</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
